--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2023_maule.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2023_maule.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>27.64575347992738</v>
+      </c>
+      <c r="C2">
         <v>32.99845336561092</v>
-      </c>
-      <c r="C2">
-        <v>27.64575347992738</v>
       </c>
       <c r="D2">
         <v>3.030445060319531</v>
       </c>
       <c r="E2">
-        <v>20.54132795298333</v>
+        <v>17.20930621949484</v>
       </c>
       <c r="F2">
         <v>62.24936582752183</v>
       </c>
       <c r="G2">
-        <v>17.20930621949484</v>
+        <v>20.54132795298333</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>28.76100819921045</v>
+      </c>
+      <c r="C3">
         <v>30.84421500151837</v>
-      </c>
-      <c r="C3">
-        <v>28.76100819921045</v>
       </c>
       <c r="D3">
         <v>3.2420990449936</v>
       </c>
       <c r="E3">
-        <v>19.32531679287644</v>
+        <v>18.02009208874006</v>
       </c>
       <c r="F3">
         <v>62.65459111838351</v>
       </c>
       <c r="G3">
-        <v>18.02009208874006</v>
+        <v>19.32531679287644</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>24.39396507882692</v>
+      </c>
+      <c r="C4">
         <v>57.21308696389219</v>
-      </c>
-      <c r="C4">
-        <v>24.39396507882692</v>
       </c>
       <c r="D4">
         <v>1.747851851851852</v>
       </c>
       <c r="E4">
-        <v>31.50378045365445</v>
+        <v>13.43227854009148</v>
       </c>
       <c r="F4">
-        <v>55.06394100625409</v>
+        <v>55.06394100625408</v>
       </c>
       <c r="G4">
-        <v>13.43227854009148</v>
+        <v>31.50378045365444</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>33.62871067789101</v>
+      </c>
+      <c r="C5">
         <v>38.45813026140895</v>
-      </c>
-      <c r="C5">
-        <v>33.62871067789101</v>
       </c>
       <c r="D5">
         <v>2.600230414746544</v>
       </c>
       <c r="E5">
+        <v>19.54170957775489</v>
+      </c>
+      <c r="F5">
+        <v>58.1101956745623</v>
+      </c>
+      <c r="G5">
         <v>22.3480947476828</v>
-      </c>
-      <c r="F5">
-        <v>58.11019567456231</v>
-      </c>
-      <c r="G5">
-        <v>19.54170957775489</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>33.15344640511678</v>
+      </c>
+      <c r="C6">
         <v>21.05248129747016</v>
-      </c>
-      <c r="C6">
-        <v>33.15344640511678</v>
       </c>
       <c r="D6">
         <v>4.750033907500339</v>
       </c>
       <c r="E6">
+        <v>21.49946302262712</v>
+      </c>
+      <c r="F6">
+        <v>64.84835018331297</v>
+      </c>
+      <c r="G6">
         <v>13.65218679405992</v>
-      </c>
-      <c r="F6">
-        <v>64.84835018331296</v>
-      </c>
-      <c r="G6">
-        <v>21.49946302262711</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>26.56415694591728</v>
+      </c>
+      <c r="C7">
         <v>39.62089077412514</v>
-      </c>
-      <c r="C7">
-        <v>26.56415694591728</v>
       </c>
       <c r="D7">
         <v>2.523921043827367</v>
       </c>
       <c r="E7">
-        <v>23.84142936906756</v>
+        <v>15.984685331419</v>
       </c>
       <c r="F7">
         <v>60.17388529951344</v>
       </c>
       <c r="G7">
-        <v>15.984685331419</v>
+        <v>23.84142936906756</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>22.57871959409044</v>
+      </c>
+      <c r="C8">
         <v>39.35233547231756</v>
-      </c>
-      <c r="C8">
-        <v>22.57871959409044</v>
       </c>
       <c r="D8">
         <v>2.541145240803944</v>
       </c>
       <c r="E8">
-        <v>24.30190765828034</v>
+        <v>13.94341535342365</v>
       </c>
       <c r="F8">
         <v>61.754676988296</v>
       </c>
       <c r="G8">
-        <v>13.94341535342365</v>
+        <v>24.30190765828034</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>27.74411443329691</v>
+      </c>
+      <c r="C9">
         <v>37.80669514254495</v>
-      </c>
-      <c r="C9">
-        <v>27.74411443329691</v>
       </c>
       <c r="D9">
         <v>2.64503415659485</v>
       </c>
       <c r="E9">
-        <v>22.83691347653906</v>
+        <v>16.75867034681387</v>
       </c>
       <c r="F9">
         <v>60.40441617664706</v>
       </c>
       <c r="G9">
-        <v>16.75867034681387</v>
+        <v>22.83691347653906</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>30.29593216983934</v>
+      </c>
+      <c r="C10">
         <v>35.57784302728383</v>
-      </c>
-      <c r="C10">
-        <v>30.29593216983934</v>
       </c>
       <c r="D10">
         <v>2.810738130563798</v>
       </c>
       <c r="E10">
-        <v>21.44874497792275</v>
+        <v>18.26444965989101</v>
       </c>
       <c r="F10">
         <v>60.28680536218624</v>
       </c>
       <c r="G10">
-        <v>18.26444965989101</v>
+        <v>21.44874497792275</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>25.14741588622962</v>
+      </c>
+      <c r="C11">
         <v>34.16579951439473</v>
-      </c>
-      <c r="C11">
-        <v>25.14741588622962</v>
       </c>
       <c r="D11">
         <v>2.926903553299492</v>
       </c>
       <c r="E11">
-        <v>21.4456782059656</v>
+        <v>15.7848900500762</v>
       </c>
       <c r="F11">
         <v>62.76943174395819</v>
       </c>
       <c r="G11">
-        <v>15.7848900500762</v>
+        <v>21.4456782059656</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>28.99862924752904</v>
+      </c>
+      <c r="C12">
         <v>42.94783926123657</v>
-      </c>
-      <c r="C12">
-        <v>28.99862924752904</v>
       </c>
       <c r="D12">
         <v>2.328405845792038</v>
       </c>
       <c r="E12">
-        <v>24.97744771015588</v>
+        <v>16.86491702855225</v>
       </c>
       <c r="F12">
         <v>58.15763526129188</v>
       </c>
       <c r="G12">
-        <v>16.86491702855225</v>
+        <v>24.97744771015588</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>28.98393791734344</v>
+      </c>
+      <c r="C13">
         <v>45.62353365818444</v>
-      </c>
-      <c r="C13">
-        <v>28.98393791734344</v>
       </c>
       <c r="D13">
         <v>2.191851265822785</v>
       </c>
       <c r="E13">
-        <v>26.12919896640827</v>
+        <v>16.59948320413437</v>
       </c>
       <c r="F13">
         <v>57.27131782945737</v>
       </c>
       <c r="G13">
-        <v>16.59948320413437</v>
+        <v>26.12919896640827</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>25.33475349969568</v>
+      </c>
+      <c r="C14">
         <v>41.49421789409617</v>
-      </c>
-      <c r="C14">
-        <v>25.33475349969568</v>
       </c>
       <c r="D14">
         <v>2.40997433076641</v>
       </c>
       <c r="E14">
-        <v>24.87230937614009</v>
+        <v>15.18606348048158</v>
       </c>
       <c r="F14">
         <v>59.94162714337833</v>
       </c>
       <c r="G14">
-        <v>15.18606348048158</v>
+        <v>24.87230937614009</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>27.82276475795555</v>
+      </c>
+      <c r="C15">
         <v>30.54745375762941</v>
-      </c>
-      <c r="C15">
-        <v>27.82276475795555</v>
       </c>
       <c r="D15">
         <v>3.273595265694588</v>
       </c>
       <c r="E15">
-        <v>19.28863522697185</v>
+        <v>17.56817981230326</v>
       </c>
       <c r="F15">
         <v>63.1431849607249</v>
       </c>
       <c r="G15">
-        <v>17.56817981230326</v>
+        <v>19.28863522697185</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>24.80696335813562</v>
+      </c>
+      <c r="C16">
         <v>44.32121297206233</v>
-      </c>
-      <c r="C16">
-        <v>24.80696335813562</v>
       </c>
       <c r="D16">
         <v>2.256255939182768</v>
       </c>
       <c r="E16">
-        <v>26.20569436374201</v>
+        <v>14.66755208765668</v>
       </c>
       <c r="F16">
         <v>59.12675354860131</v>
       </c>
       <c r="G16">
-        <v>14.66755208765668</v>
+        <v>26.20569436374201</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>26.18054030309686</v>
+      </c>
+      <c r="C17">
         <v>41.59894575005491</v>
-      </c>
-      <c r="C17">
-        <v>26.18054030309686</v>
       </c>
       <c r="D17">
         <v>2.403907074973601</v>
       </c>
       <c r="E17">
-        <v>24.79382118078283</v>
+        <v>15.60413666710303</v>
       </c>
       <c r="F17">
-        <v>59.60204215211416</v>
+        <v>59.60204215211415</v>
       </c>
       <c r="G17">
-        <v>15.60413666710303</v>
+        <v>24.79382118078282</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>28.84732020301976</v>
+      </c>
+      <c r="C18">
         <v>35.02410061608197</v>
-      </c>
-      <c r="C18">
-        <v>28.84732020301976</v>
       </c>
       <c r="D18">
         <v>2.855176813707619</v>
       </c>
       <c r="E18">
-        <v>21.37291569269129</v>
+        <v>17.60363098020882</v>
       </c>
       <c r="F18">
         <v>61.02345332709989</v>
       </c>
       <c r="G18">
-        <v>17.60363098020882</v>
+        <v>21.37291569269129</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>28.93995552260934</v>
+      </c>
+      <c r="C19">
         <v>39.30318754633061</v>
-      </c>
-      <c r="C19">
-        <v>28.93995552260934</v>
       </c>
       <c r="D19">
         <v>2.544322897019992</v>
       </c>
       <c r="E19">
-        <v>23.36094465985196</v>
+        <v>17.20126894606979</v>
       </c>
       <c r="F19">
         <v>59.43778639407825</v>
       </c>
       <c r="G19">
-        <v>17.20126894606979</v>
+        <v>23.36094465985196</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>26.12190743775853</v>
+      </c>
+      <c r="C20">
         <v>32.0533832826036</v>
-      </c>
-      <c r="C20">
-        <v>26.12190743775853</v>
       </c>
       <c r="D20">
         <v>3.119795471146822</v>
       </c>
       <c r="E20">
-        <v>20.26446933438595</v>
+        <v>16.51453101100311</v>
       </c>
       <c r="F20">
         <v>63.22099965461095</v>
       </c>
       <c r="G20">
-        <v>16.51453101100311</v>
+        <v>20.26446933438595</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>25.58211256746338</v>
+      </c>
+      <c r="C21">
         <v>36.73091750192752</v>
-      </c>
-      <c r="C21">
-        <v>25.58211256746338</v>
       </c>
       <c r="D21">
         <v>2.722502099076406</v>
       </c>
       <c r="E21">
-        <v>22.6296788903667</v>
+        <v>15.76097282918488</v>
       </c>
       <c r="F21">
-        <v>61.60934828044841</v>
+        <v>61.60934828044842</v>
       </c>
       <c r="G21">
-        <v>15.76097282918487</v>
+        <v>22.62967889036671</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>27.42341047878072</v>
+      </c>
+      <c r="C22">
         <v>36.27546569507876</v>
-      </c>
-      <c r="C22">
-        <v>27.42341047878072</v>
       </c>
       <c r="D22">
         <v>2.756684113736031</v>
       </c>
       <c r="E22">
-        <v>22.15987460815047</v>
+        <v>16.75235109717868</v>
       </c>
       <c r="F22">
         <v>61.08777429467084</v>
       </c>
       <c r="G22">
-        <v>16.75235109717868</v>
+        <v>22.15987460815047</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>24.82858173944425</v>
+      </c>
+      <c r="C23">
         <v>47.34752796824252</v>
-      </c>
-      <c r="C23">
-        <v>24.82858173944425</v>
       </c>
       <c r="D23">
         <v>2.112042682926829</v>
       </c>
       <c r="E23">
-        <v>27.49947600083841</v>
+        <v>14.42045692726892</v>
       </c>
       <c r="F23">
         <v>58.08006707189269</v>
       </c>
       <c r="G23">
-        <v>14.42045692726892</v>
+        <v>27.49947600083841</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>27.90201866595104</v>
+      </c>
+      <c r="C24">
         <v>35.26105495422966</v>
-      </c>
-      <c r="C24">
-        <v>27.90201866595104</v>
       </c>
       <c r="D24">
         <v>2.83599002156357</v>
       </c>
       <c r="E24">
-        <v>21.6109283625731</v>
+        <v>17.10069444444445</v>
       </c>
       <c r="F24">
         <v>61.28837719298246</v>
       </c>
       <c r="G24">
-        <v>17.10069444444445</v>
+        <v>21.6109283625731</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>30.7475884244373</v>
+      </c>
+      <c r="C25">
         <v>37.01768488745981</v>
-      </c>
-      <c r="C25">
-        <v>30.7475884244373</v>
       </c>
       <c r="D25">
         <v>2.701411509229099</v>
       </c>
       <c r="E25">
-        <v>22.06516530905606</v>
+        <v>18.32774317201725</v>
       </c>
       <c r="F25">
         <v>59.60709151892669</v>
       </c>
       <c r="G25">
-        <v>18.32774317201725</v>
+        <v>22.06516530905606</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>27.12409886714727</v>
+      </c>
+      <c r="C26">
         <v>35.74922760041195</v>
-      </c>
-      <c r="C26">
-        <v>27.12409886714727</v>
       </c>
       <c r="D26">
         <v>2.797263233705438</v>
       </c>
       <c r="E26">
-        <v>21.94909895668669</v>
+        <v>16.65349351881126</v>
       </c>
       <c r="F26">
         <v>61.39740752450205</v>
       </c>
       <c r="G26">
-        <v>16.65349351881126</v>
+        <v>21.94909895668669</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>28.70522125965816</v>
+      </c>
+      <c r="C27">
         <v>38.53563902732716</v>
-      </c>
-      <c r="C27">
-        <v>28.70522125965816</v>
       </c>
       <c r="D27">
         <v>2.595000433990105</v>
       </c>
       <c r="E27">
+        <v>17.164</v>
+      </c>
+      <c r="F27">
+        <v>59.79399999999999</v>
+      </c>
+      <c r="G27">
         <v>23.042</v>
-      </c>
-      <c r="F27">
-        <v>59.794</v>
-      </c>
-      <c r="G27">
-        <v>17.164</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>29.47775053859297</v>
+      </c>
+      <c r="C28">
         <v>39.68501597206745</v>
-      </c>
-      <c r="C28">
-        <v>29.47775053859297</v>
       </c>
       <c r="D28">
         <v>2.519842755522276</v>
       </c>
       <c r="E28">
-        <v>23.45966360721971</v>
+        <v>17.42567300513812</v>
       </c>
       <c r="F28">
         <v>59.11466338764218</v>
       </c>
       <c r="G28">
-        <v>17.42567300513812</v>
+        <v>23.45966360721971</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>30.72921622736067</v>
+      </c>
+      <c r="C29">
         <v>35.66784026390079</v>
-      </c>
-      <c r="C29">
-        <v>30.72921622736067</v>
       </c>
       <c r="D29">
         <v>2.803646064917741</v>
       </c>
       <c r="E29">
-        <v>21.43537933663744</v>
+        <v>18.46740373617995</v>
       </c>
       <c r="F29">
         <v>60.09721692718261</v>
       </c>
       <c r="G29">
-        <v>18.46740373617995</v>
+        <v>21.43537933663744</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>30.823264962068</v>
+      </c>
+      <c r="C30">
         <v>41.09768661609066</v>
-      </c>
-      <c r="C30">
-        <v>30.823264962068</v>
       </c>
       <c r="D30">
         <v>2.433226982680036</v>
       </c>
       <c r="E30">
-        <v>23.90499019394203</v>
+        <v>17.92874264545652</v>
       </c>
       <c r="F30">
         <v>58.16626716060143</v>
       </c>
       <c r="G30">
-        <v>17.92874264545652</v>
+        <v>23.90499019394203</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>28.78717830174141</v>
+      </c>
+      <c r="C31">
         <v>35.39836646632763</v>
-      </c>
-      <c r="C31">
-        <v>28.78717830174141</v>
       </c>
       <c r="D31">
         <v>2.824989116238572</v>
       </c>
       <c r="E31">
-        <v>21.55997747324949</v>
+        <v>17.53332081847194</v>
       </c>
       <c r="F31">
         <v>60.90670170827859</v>
       </c>
       <c r="G31">
-        <v>17.53332081847194</v>
+        <v>21.55997747324949</v>
       </c>
     </row>
   </sheetData>
